--- a/JsonConverter/ExcelFiles/AbsorbTargetData.xlsx
+++ b/JsonConverter/ExcelFiles/AbsorbTargetData.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Target_01</t>
   </si>
   <si>
-    <t xml:space="preserve">행인</t>
+    <t xml:space="preserve">행인(남성)</t>
   </si>
   <si>
     <t xml:space="preserve">Target_Person</t>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Target_02</t>
   </si>
   <si>
-    <t xml:space="preserve">강아지</t>
+    <t xml:space="preserve">행인(여성)</t>
   </si>
   <si>
     <t xml:space="preserve">Target_03</t>
@@ -143,7 +143,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -228,6 +228,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="0"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -290,7 +297,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -337,6 +344,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -719,7 +730,7 @@
       <c r="A5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="12" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="8" t="n">
